--- a/list_dashboard.xlsx
+++ b/list_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\X13 YOGA\Desktop\Magang Mandiri\project1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A13B705-1167-4C05-9122-695AF476CB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90468DBA-6B0F-4FFB-9FDC-6018DEA754AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{5E1F8ADB-4C48-43D9-915E-AC728F0C8112}"/>
   </bookViews>
@@ -661,16 +661,16 @@
     <t>Connector 2</t>
   </si>
   <si>
+    <t>https://monitoring.ilcs.co.id/d/df07rysvmjx1cc/vm-linux?var-interval=1m&amp;orgId=1&amp;from=2026-03-31T17:00:00.000Z&amp;to=2026-04-07T16:59:59.000Z&amp;timezone=browser&amp;var-prome_ds=eey4rwzgb9ibke&amp;var-job=node-exporter&amp;var-nodename=svrlpccon01&amp;var-instance=10.174.1.54:9100</t>
+  </si>
+  <si>
+    <t>https://monitoring.ilcs.co.id/d/df07rysvmjx1cc/vm-linux?var-interval=1m&amp;orgId=1&amp;from=2026-03-31T17:00:00.000Z&amp;to=2026-04-07T16:59:59.000Z&amp;timezone=browser&amp;var-prome_ds=eey4rwzgb9ibke&amp;var-job=node-exporter&amp;var-nodename=svrlpccon02&amp;var-instance=10.174.1.54:9100</t>
+  </si>
+  <si>
+    <t>VM Connector</t>
+  </si>
+  <si>
     <t>Connector 1</t>
-  </si>
-  <si>
-    <t>VM Linux</t>
-  </si>
-  <si>
-    <t>https://monitoring.ilcs.co.id/d/df07rysvmjx1cc/vm-linux?var-interval=1m&amp;orgId=1&amp;from=2026-03-31T17:00:00.000Z&amp;to=2026-04-07T16:59:59.000Z&amp;timezone=browser&amp;var-prome_ds=eey4rwzgb9ibke&amp;var-job=node-exporter&amp;var-nodename=svrlpccon01&amp;var-instance=10.174.1.54:9100</t>
-  </si>
-  <si>
-    <t>https://monitoring.ilcs.co.id/d/df07rysvmjx1cc/vm-linux?var-interval=1m&amp;orgId=1&amp;from=2026-03-31T17:00:00.000Z&amp;to=2026-04-07T16:59:59.000Z&amp;timezone=browser&amp;var-prome_ds=eey4rwzgb9ibke&amp;var-job=node-exporter&amp;var-nodename=svrlpccon02&amp;var-instance=10.174.1.54:9100</t>
   </si>
 </sst>
 </file>
@@ -1723,13 +1723,13 @@
         <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="F29" s="2">
         <v>470</v>
@@ -1743,13 +1743,13 @@
         <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F30" s="2">
         <v>470</v>
